--- a/Control_Insumos.xlsx
+++ b/Control_Insumos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\ANALISIS INSUMOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899EA30B-8F57-4B3C-A2BF-0CD45E6C9F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BD5EC4-31A3-4740-9979-E24E37059A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-2024" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="71">
   <si>
     <t>GENERACIÓN DE RESIDUOS</t>
   </si>
@@ -261,7 +261,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +342,11 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4659,7 +4664,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblFactSolped" displayName="tblFactSolped" ref="A1:F81" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tblFactSolped" displayName="tblFactSolped" ref="A1:F111" dataDxfId="6">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Año" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Mes" dataDxfId="4"/>
@@ -6179,7 +6184,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="7" width="13.81640625" customWidth="1"/>
@@ -7805,7 +7810,534 @@
         <v>67</v>
       </c>
     </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B82" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="30">
+        <v>46114</v>
+      </c>
+      <c r="D82" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E82" s="31"/>
+      <c r="F82" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B83" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="30">
+        <v>46115</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E83" s="31"/>
+      <c r="F83" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B84" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="30">
+        <v>46116</v>
+      </c>
+      <c r="D84" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="31"/>
+      <c r="F84" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B85" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="30">
+        <v>46117</v>
+      </c>
+      <c r="D85" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E85" s="31"/>
+      <c r="F85" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B86" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="30">
+        <v>46118</v>
+      </c>
+      <c r="D86" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E86" s="31"/>
+      <c r="F86" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B87" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="30">
+        <v>46119</v>
+      </c>
+      <c r="D87" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E87" s="31"/>
+      <c r="F87" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B88" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="30">
+        <v>46120</v>
+      </c>
+      <c r="D88" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E88" s="31"/>
+      <c r="F88" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B89" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="30">
+        <v>46121</v>
+      </c>
+      <c r="D89" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="31"/>
+      <c r="F89" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B90" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="30">
+        <v>46122</v>
+      </c>
+      <c r="D90" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E90" s="31"/>
+      <c r="F90" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B91" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="30">
+        <v>46123</v>
+      </c>
+      <c r="D91" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E91" s="31"/>
+      <c r="F91" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B92" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="30">
+        <v>46124</v>
+      </c>
+      <c r="D92" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E92" s="31">
+        <v>498311</v>
+      </c>
+      <c r="F92" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B93" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="30">
+        <v>46125</v>
+      </c>
+      <c r="D93" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E93" s="31">
+        <v>512878</v>
+      </c>
+      <c r="F93" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B94" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="30">
+        <v>46126</v>
+      </c>
+      <c r="D94" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="31">
+        <v>38679</v>
+      </c>
+      <c r="F94" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B95" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" s="30">
+        <v>46127</v>
+      </c>
+      <c r="D95" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="31">
+        <v>49721</v>
+      </c>
+      <c r="F95" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B96" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" s="30">
+        <v>46128</v>
+      </c>
+      <c r="D96" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E96" s="31">
+        <v>709205</v>
+      </c>
+      <c r="F96" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B97" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" s="30">
+        <v>46129</v>
+      </c>
+      <c r="D97" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E97" s="31">
+        <v>367760</v>
+      </c>
+      <c r="F97" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B98" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="30">
+        <v>46130</v>
+      </c>
+      <c r="D98" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E98" s="31">
+        <v>274414</v>
+      </c>
+      <c r="F98" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B99" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" s="30">
+        <v>46131</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="31">
+        <v>68577</v>
+      </c>
+      <c r="F99" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B100" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="30">
+        <v>46132</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="31">
+        <v>9794</v>
+      </c>
+      <c r="F100" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B101" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" s="30">
+        <v>46133</v>
+      </c>
+      <c r="D101" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E101" s="31"/>
+      <c r="F101" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B102" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="30">
+        <v>46134</v>
+      </c>
+      <c r="D102" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E102" s="31">
+        <v>409382</v>
+      </c>
+      <c r="F102" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B103" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103" s="30">
+        <v>46135</v>
+      </c>
+      <c r="D103" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E103" s="31">
+        <v>442180</v>
+      </c>
+      <c r="F103" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B104" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" s="30">
+        <v>46136</v>
+      </c>
+      <c r="D104" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="E104" s="31">
+        <v>88829</v>
+      </c>
+      <c r="F104" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B105" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105" s="30">
+        <v>46137</v>
+      </c>
+      <c r="D105" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="31"/>
+      <c r="F105" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="29">
+        <v>2026</v>
+      </c>
+      <c r="B106" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" s="30">
+        <v>46138</v>
+      </c>
+      <c r="D106" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E106" s="31">
+        <v>641367</v>
+      </c>
+      <c r="F106" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="29"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="30"/>
+      <c r="D107" s="29"/>
+      <c r="E107" s="31"/>
+      <c r="F107" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="29"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="30"/>
+      <c r="D108" s="29"/>
+      <c r="E108" s="31"/>
+      <c r="F108" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="29"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="30"/>
+      <c r="D109" s="29"/>
+      <c r="E109" s="31"/>
+      <c r="F109" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="29"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="30"/>
+      <c r="D110" s="29"/>
+      <c r="E110" s="31"/>
+      <c r="F110" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="29"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="30"/>
+      <c r="D111" s="29"/>
+      <c r="E111" s="31"/>
+      <c r="F111" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
